--- a/docs/mba8660-decision-tools.xlsx
+++ b/docs/mba8660-decision-tools.xlsx
@@ -87,6 +87,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/docs/mba8660-decision-tools.xlsx
+++ b/docs/mba8660-decision-tools.xlsx
@@ -15,7 +15,11 @@
     <sheet name="Week 10" sheetId="11" r:id="rId11"/>
     <sheet name="Week 11" sheetId="12" r:id="rId12"/>
     <sheet name="Week 12" sheetId="13" r:id="rId13"/>
-    <sheet name="Rates" sheetId="14" r:id="rId14"/>
+    <sheet name="Module 1" sheetId="14" r:id="rId14"/>
+    <sheet name="Module 2" sheetId="15" r:id="rId15"/>
+    <sheet name="Module 3" sheetId="16" r:id="rId16"/>
+    <sheet name="Final Project" sheetId="17" r:id="rId17"/>
+    <sheet name="Rates" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -109,7 +113,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated 2026-09-12 from the MBA 8660 Decision Tools application.</t>
+          <t xml:space="preserve">Generated 2026-09-13 from the MBA 8660 Decision Tools application.</t>
         </is>
       </c>
     </row>
@@ -806,7 +810,7 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="B27" s="4">
         <f>ROUND($B$16-$B$6,0)</f>
-        <v>-587</v>
+        <v>-588</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -1214,7 +1218,7 @@
       </c>
       <c r="B28" s="4">
         <f>ROUND($B$17-$B$6,0)</f>
-        <v>-406</v>
+        <v>-407</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
@@ -1240,7 +1244,7 @@
       </c>
       <c r="B29" s="4">
         <f>ROUND($B$18-$B$6,0)</f>
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="B30" s="4">
         <f>ROUND($B$19-$B$6,0)</f>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -1292,7 +1296,7 @@
       </c>
       <c r="B31" s="4">
         <f>ROUND($B$20-$B$6,0)</f>
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -1318,7 +1322,7 @@
       </c>
       <c r="B32" s="4">
         <f>ROUND($B$21-$B$6,0)</f>
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -1344,7 +1348,7 @@
       </c>
       <c r="B33" s="4">
         <f>ROUND($B$22-$B$6,0)</f>
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1400,7 @@
       </c>
       <c r="B35" s="4">
         <f>$B$32</f>
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="B36" s="4">
         <f>IF($B$35&gt;0,$B$11/($B$35/$B$23),$B$11)</f>
-        <v>14.125560538116591</v>
+        <v>14.157303370786517</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -2970,6 +2974,2904 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 13: Module 1: Platform Architecture Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidate Weeks 1 to 4 into one architecture recommendation: storage, table format, catalog, and engine, with a stated lock-in position and a three-year cost that lives inside the ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUTS YOU SUPPLY</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change any figure in column B. Every computed cell below recalculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case organization</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meridian Health Partners</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The organization every figure belongs to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Architecture path</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distributed</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 1 recommendation: single node or distributed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Table format</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iceberg</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 2 recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalog</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managed Iceberg REST catalog</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 3 recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snowflake Standard</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 4 recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year-three working set</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>616.5</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GiB</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carried from Week 1, grown at your stated rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-node memory ceiling</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>512</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GiB</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The largest single machine you are willing to rent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priced exit cost</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <v>1411</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rewrite compute plus egress, from Week 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalog annual cost</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <v>17000</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 3 objects and requests, plus the licence or self-hosting salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine annual cost</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>172800</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compute after any committed-use discount, from Week 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Storage annual cost</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <v>96600</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Week 4. It grows whether or not anyone queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <v>850000</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The constraint the artifact fails against. It does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual growth</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <v>22</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compounded across the horizon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queries per year</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <v>328500</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">queries</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The denominator for cost per query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizon</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <v>3</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">years</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three, to match the Final Project Artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATES AND CONSTANTS</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published list prices link to the Rates sheet. Change a price there and every week that uses it follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source and note</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPUTED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each cell holds the formula shown in column D. Nothing here is typed in by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figure</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation in words</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-node headroom in year three</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>$B$12/$B$11</f>
+        <v>0.8304947283049473</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-node memory ceiling ÷ Year-three working set</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Below 1.0 the single-node path has run out of capacity, which decides the architecture for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate</t>
+        </is>
+      </c>
+      <c r="B28" s="5">
+        <f>$B$15+$B$16+$B$14</f>
+        <v>286400</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine annual cost + Storage annual cost + Catalog annual cost</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The three architecture layers added up, before anything Module 2 does to them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalog share of the platform bill</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>$B$14/$B$28*100</f>
+        <v>5.935754189944134</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalog annual cost ÷ Platform run rate × 100</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The smallest line and the largest blast radius. Price is not a measure of importance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform cost per query</t>
+        </is>
+      </c>
+      <c r="B30" s="6">
+        <f>$B$28/$B$19</f>
+        <v>0.871841704718417</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate ÷ Queries per year</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The run rate in the unit a business owner acts on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final-year platform cost</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>$B$28*(1+$B$18/100)^($B$20-1)</f>
+        <v>426277.76</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate × (1 + Annual growth ÷ 100) ^ (Horizon - 1)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The run rate after growth compounds. The ceiling it is measured against did not move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform total across the horizon</t>
+        </is>
+      </c>
+      <c r="B32" s="5">
+        <f>IF($B$18=0,$B$28*$B$20,$B$28*((1+$B$18/100)^$B$20-1)/($B$18/100))</f>
+        <v>1062085.76</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IF(Annual growth=0,Platform run rate × Horizon,Platform run rate × ((1 + Annual growth ÷ 100) ^ Horizon - 1) ÷ (Annual growth ÷ 100))</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The geometric series. Change the growth rate or the horizon and watch which one is deciding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Budget remaining in year one</t>
+        </is>
+      </c>
+      <c r="B33" s="5">
+        <f>$B$17-$B$28</f>
+        <v>563600</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling - Platform run rate</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative means the artifact fails before Module 2 adds anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceiling utilisation in year one</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>$B$28/$B$17*100</f>
+        <v>33.694117647058825</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate ÷ Annual budget ceiling × 100</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How much of the ceiling the architecture alone consumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priced exit, in months of run rate</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>$B$13/($B$28/12)</f>
+        <v>0.059120111731843575</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">months</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priced exit cost ÷ (Platform run rate ÷ 12)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The honest unit for a lock-in argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priced exit as a share of the horizon total</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>$B$13/$B$32*100</f>
+        <v>0.13285179532018207</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priced exit cost ÷ Platform total across the horizon × 100</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What leaving costs against what staying costs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 14: Module 2: Cost Model and Reliability Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidate Weeks 5 to 7 into one operating cost model: what the cut removed, what the ingestion decision changed, and what the reliability control you would fund costs per year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUTS YOU SUPPLY</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change any figure in column B. Every computed cell below recalculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability control</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freshness SLA monitor on the claims table</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The one control you would fund, from Week 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingestion path</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 6 decision: build or buy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total annual platform spend</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <v>662600</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The whole platform bill Week 5 cut against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual saving</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <v>128160</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What the Week 5 cut plan removes, summed across categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target reduction</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <v>20</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The mandate. The syllabus sets it at 20 percent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chosen ingestion path, annual cost</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>108000</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 6 path you chose, at twelve months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingestion already counted in platform spend</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>120000</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ingestion category inside Week 5's total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Break-even</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <v>35</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">months</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Week 6. Compare it against the horizon before reading it as a verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control steady-state annual cost</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <v>61440</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooling plus operating effort, from Week 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exposure avoided</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>360000</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual exposure times your estimated catch rate, from Week 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <v>850000</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged from Module 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queries per year</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <v>328500</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">queries</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The denominator for cost per query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual growth</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <v>22</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applied to the operating run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizon</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <v>3</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">years</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three, to match the Final Project Artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATES AND CONSTANTS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published list prices link to the Rates sheet. Change a price there and every week that uses it follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source and note</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPUTED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each cell holds the formula shown in column D. Nothing here is typed in by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figure</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation in words</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform spend after the cut</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>$B$8-$B$9</f>
+        <v>534440</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total annual platform spend - Annual saving</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 5 total minus the Week 5 saving. The starting point for everything below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reduction achieved</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>$B$9/$B$8*100</f>
+        <v>19.34198611530335</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual saving ÷ Total annual platform spend × 100</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The saving as a share of total spend, against the mandate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingestion delta against what was already counted</t>
+        </is>
+      </c>
+      <c r="B28" s="5">
+        <f>$B$11-$B$12</f>
+        <v>-12000</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chosen ingestion path, annual cost - Ingestion already counted in platform spend</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The line that prevents double counting. Negative releases spend, positive adds it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability control, per year</t>
+        </is>
+      </c>
+      <c r="B29" s="5">
+        <f>$B$14</f>
+        <v>61440</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control steady-state annual cost</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New spend rather than reconciled spend, so it is added rather than netted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating run rate</t>
+        </is>
+      </c>
+      <c r="B30" s="5">
+        <f>$B$26+$B$28+$B$29</f>
+        <v>583880</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform spend after the cut + Ingestion delta against what was already counted + Reliability control, per year</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What Module 3 and the Final Artifact carry forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Net change against the Week 5 baseline</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>$B$8-$B$30</f>
+        <v>78720</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total annual platform spend - Operating run rate</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What the whole module actually moved, control included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Share of the cut consumed by the control</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>$B$29/$B$9*100</f>
+        <v>47.940074906367045</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability control, per year ÷ Annual saving × 100</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Above 100 percent the cut funded the control and nothing else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Net reliability position</t>
+        </is>
+      </c>
+      <c r="B33" s="5">
+        <f>$B$15-$B$29</f>
+        <v>298560</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exposure avoided - Reliability control, per year</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive is not the same as fundable, and it never was.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating cost per query</t>
+        </is>
+      </c>
+      <c r="B34" s="6">
+        <f>$B$30/$B$17</f>
+        <v>1.7774124809741247</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating run rate ÷ Queries per year</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compare it against the Module 1 figure to see what this module bought.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final-year operating run rate</t>
+        </is>
+      </c>
+      <c r="B35" s="5">
+        <f>$B$30*(1+$B$18/100)^($B$19-1)</f>
+        <v>869046.992</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating run rate × (1 + Annual growth ÷ 100) ^ (Horizon - 1)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The cut was a one-time step down on a curve that keeps rising.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating total across the horizon</t>
+        </is>
+      </c>
+      <c r="B36" s="5">
+        <f>IF($B$18=0,$B$30*$B$19,$B$30*((1+$B$18/100)^$B$19-1)/($B$18/100))</f>
+        <v>2165260.5919999997</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IF(Annual growth=0,Operating run rate × Horizon,Operating run rate × ((1 + Annual growth ÷ 100) ^ Horizon - 1) ÷ (Annual growth ÷ 100))</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every year grown and added. Carried into the Final Project Artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Budget remaining in year one</t>
+        </is>
+      </c>
+      <c r="B37" s="5">
+        <f>$B$16-$B$30</f>
+        <v>266120</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling - Operating run rate</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance is still to come in Module 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceiling utilisation in year one</t>
+        </is>
+      </c>
+      <c r="B38" s="4">
+        <f>$B$30/$B$16*100</f>
+        <v>68.69176470588235</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating run rate ÷ Annual budget ceiling × 100</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How much of the ceiling operations consume before any governance cost is counted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 15: Module 3: Governance and Regulatory Exposure Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidate Weeks 8 to 12 into one governance position: an operating model, a US state privacy path, an EU AI Act exposure statement with dates, and an agent access policy, each with its annual cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUTS YOU SUPPLY</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change any figure in column B. Every computed cell below recalculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating model</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centralized</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 8 decision: centralized or federated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy path</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State by state</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 9 decision: one national standard or state by state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role under the AI Act</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployer</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 10 classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent authentication method</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Short-lived vended credential</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 12 decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent grant over personal data</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whether the agent may read tables containing personal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance staffing, annual</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>1140000</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fully loaded headcount cost for the operating model you chose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy programme build</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>440000</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-time cost of the Week 9 path you chose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy programme, annual</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <v>192000</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ongoing programme cost on that same path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Act readiness cost</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <v>360000</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Readiness hours times a blended rate, from Week 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days until Annex III applies</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>445</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the Week 10 timeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retrieval corpus, annual</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <v>2746</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Embedding plus vector storage plus answer generation, from Week 11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deletion request SLA</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <v>45</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What you have promised, statutorily or contractually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reindex interval</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <v>30</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How often the index is rebuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent read spend, annual</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <v>1470</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Week 12, at the same per-TB rate a human pays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operating run rate from Module 2</t>
+        </is>
+      </c>
+      <c r="B20" s="4">
+        <v>583880</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The denominator for every share on this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizon</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">years</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three, to match the Final Project Artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATES AND CONSTANTS</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published list prices link to the Rates sheet. Change a price there and every week that uses it follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source and note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPUTED</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each cell holds the formula shown in column D. Nothing here is typed in by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figure</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation in words</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance run rate</t>
+        </is>
+      </c>
+      <c r="B28" s="5">
+        <f>$B$11+$B$13+$B$16+$B$19</f>
+        <v>1336216</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance staffing, annual + Privacy programme, annual + Retrieval corpus, annual + Agent read spend, annual</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The recurring cost of being allowed to operate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staffing share of governance</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>$B$11/$B$28*100</f>
+        <v>85.31554778568734</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance staffing, annual ÷ Governance run rate × 100</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance is an organizational decision priced as an architectural one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-time readiness investment</t>
+        </is>
+      </c>
+      <c r="B30" s="5">
+        <f>$B$12+$B$14</f>
+        <v>800000</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy programme build + AI Act readiness cost</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paid once, in year one, on top of the run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance total across the horizon</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>$B$28*$B$21+$B$30</f>
+        <v>4808648</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance run rate × Horizon + One-time readiness investment</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run rate times the horizon plus the one-time investment. Held flat deliberately: staffing does not compound the way a query bill does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance as a share of total run rate</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>$B$28/($B$28+$B$20)*100</f>
+        <v>69.59110377814443</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance run rate ÷ (Governance run rate + Operating run rate from Module 2) × 100</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Above 50 percent the platform is the cheaper half of the platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance per dollar of operations</t>
+        </is>
+      </c>
+      <c r="B33" s="4">
+        <f>$B$28/$B$20</f>
+        <v>2.2885113379461535</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance run rate ÷ Operating run rate from Module 2</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State whether your organization knows this ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weeks until Annex III applies</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>$B$15/7</f>
+        <v>63.57142857142857</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weeks</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days until Annex III applies ÷ 7</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Working time remaining before the deferred high-risk obligations take effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Readiness spend per remaining week</t>
+        </is>
+      </c>
+      <c r="B35" s="5">
+        <f>$B$14/$B$34</f>
+        <v>5662.921348314607</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per week</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Act readiness cost ÷ Weeks until Annex III applies</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If nobody has budgeted this, the deferral bought less than it appeared to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deletion promise against reindex interval</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>$B$17-$B$18</f>
+        <v>15</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deletion request SLA - Reindex interval</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive means deleted records stay retrievable past the date you promised they would be gone.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 16: Final Project Artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assemble all three modules into one three-year cost of ownership, test it against the budget ceiling that fails the artifact, and commit in writing to the architecture you rejected and the recommendation most likely to be wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INPUTS YOU SUPPLY</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change any figure in column B. Every computed cell below recalculates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case organization</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meridian Health Partners</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assigned in Week 1, carried through every module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate after the cut</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <v>534440</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Module 2, carried forward rather than recomputed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ingestion, annual</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <v>108000</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 6 path you chose, at its full annual cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability control, annual</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <v>61440</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Week 7 control you would fund, at steady state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance, annual</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <v>1336216</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From Module 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-time investment</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <v>800000</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy build, AI Act readiness, and any ingestion build. Lands entirely in year one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <v>2900000</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The constraint the artifact fails against. It does not grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual growth</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <v>22</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applied to every recurring stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Queries per year</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <v>328500</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">queries</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The denominator for both cost-per-query figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horizon</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">years</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three, as the Final Project Artifact requires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Architecture considered and rejected</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-node DuckDB on one 512 GiB machine with Parquet on object storage</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required by the syllabus. An option you actually costed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason for rejection</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the year-three working set of 616 GiB exceeds the largest single node we are willing to rent</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One clause, as the syllabus requires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recommendation most likely to be wrong</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 60 percent catch rate on the freshness monitor. It is my estimate rather than a measurement, and the entire net reliability position rests on it.</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required by the syllabus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence that would change your mind</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two consecutive quarters in which the monitor catches under 40 percent of freshness incidents logged by the on-call team. At that point the control is repriced or replaced at the March review.</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The observation that reverses the decision above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATES AND CONSTANTS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Published list prices link to the Rates sheet. Change a price there and every week that uses it follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source and note</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPUTED</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each cell holds the formula shown in column D. Nothing here is typed in by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figure</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation in words</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual run rate</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>$B$7+$B$8+$B$9+$B$10</f>
+        <v>2040096</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Platform run rate after the cut + Ingestion, annual + Reliability control, annual + Governance, annual</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What the recommendation costs every year, forever, excluding the one-time investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year one total</t>
+        </is>
+      </c>
+      <c r="B27" s="5">
+        <f>$B$26+$B$11</f>
+        <v>2840096</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual run rate + One-time investment</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run rate plus the one-time investment. The figure the ceiling is tested against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceiling verdict</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="str">
+        <f>IF($B$12-$B$27&gt;=0,"Inside the ceiling","Breaches the ceiling")</f>
+        <v>Inside the ceiling</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IF(Annual budget ceiling - Year one total&gt;=0,"Inside the ceiling","Breaches the ceiling")</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The syllabus is explicit: exceed the stated annual budget ceiling and the artifact fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headroom in year one</t>
+        </is>
+      </c>
+      <c r="B29" s="5">
+        <f>$B$12-$B$27</f>
+        <v>59904</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling - Year one total</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative is the amount by which the artifact fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ceiling utilisation in year one</t>
+        </is>
+      </c>
+      <c r="B30" s="4">
+        <f>$B$27/$B$12*100</f>
+        <v>97.9343448275862</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year one total ÷ Annual budget ceiling × 100</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Above about 95 percent there is no room for a price change you do not control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-time share of year one</t>
+        </is>
+      </c>
+      <c r="B31" s="4">
+        <f>$B$11/$B$27*100</f>
+        <v>28.168061924667338</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One-time investment ÷ Year one total × 100</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A high share means year one misrepresents the commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance share of the run rate</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>$B$10/$B$26*100</f>
+        <v>65.49770206892225</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance, annual ÷ Annual run rate × 100</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carried from Module 3 and usually the largest single stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final-year run rate</t>
+        </is>
+      </c>
+      <c r="B33" s="5">
+        <f>$B$26*(1+$B$13/100)^($B$15-1)</f>
+        <v>3036478.8863999997</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD per year</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual run rate × (1 + Annual growth ÷ 100) ^ (Horizon - 1)</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The run rate after growth compounds across the horizon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headroom in the final year</t>
+        </is>
+      </c>
+      <c r="B34" s="5">
+        <f>$B$12-$B$33</f>
+        <v>-136478.88639999973</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annual budget ceiling - Final-year run rate</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The same ceiling against the final-year run rate. The figure a reviewer checks second.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total cost of ownership across the horizon</t>
+        </is>
+      </c>
+      <c r="B35" s="5">
+        <f>IF($B$13=0,$B$26*$B$15,$B$26*((1+$B$13/100)^$B$15-1)/($B$13/100))+$B$11</f>
+        <v>8365492.006399999</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IF(Annual growth=0,Annual run rate × Horizon,Annual run rate × ((1 + Annual growth ÷ 100) ^ Horizon - 1) ÷ (Annual growth ÷ 100)) + One-time investment</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every year grown and added, plus the one-time investment. The headline number of the artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost per query in year one</t>
+        </is>
+      </c>
+      <c r="B36" s="6">
+        <f>$B$27/$B$14</f>
+        <v>8.6456499238965</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Year one total ÷ Queries per year</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The artifact denominated in the unit a business owner recognizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost per query in the final year</t>
+        </is>
+      </c>
+      <c r="B37" s="6">
+        <f>$B$33/$B$14</f>
+        <v>9.243466929680364</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final-year run rate ÷ Queries per year</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If this falls while total spend rises, the platform is getting more efficient. Say so, because the total will not.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
